--- a/hw2fintools/xlsx/DivCalc.xlsx
+++ b/hw2fintools/xlsx/DivCalc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harveywargo/Desktop/GithubProjects/hw2fintools/hw2fintools/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1F8DD0-093E-0F4F-920A-5D3A84D6088F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DE2588-B47F-6740-A457-1A3E95A9B941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{0A3F2C1F-1553-164F-8D8B-0E0EBB5D09A0}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28040" windowHeight="17180" xr2:uid="{0A3F2C1F-1553-164F-8D8B-0E0EBB5D09A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A0B48E0-DEE3-9E45-A564-5FB8FF4BAEE7}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
@@ -477,7 +477,7 @@
       </c>
       <c r="H1" s="3">
         <f>B2/B5</f>
-        <v>162.28571428571425</v>
+        <v>167.35294117647058</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -485,14 +485,14 @@
         <v>0</v>
       </c>
       <c r="B2" s="3">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3">
-        <f>B18/B1</f>
-        <v>408.66666666666669</v>
+        <f>B19/B1</f>
+        <v>409.33333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -506,8 +506,8 @@
         <v>6</v>
       </c>
       <c r="H3" s="3">
-        <f>B19</f>
-        <v>88.82</v>
+        <f>B20</f>
+        <v>89.02000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -522,7 +522,7 @@
       </c>
       <c r="H4" s="3">
         <f>SUM(H2:H3)</f>
-        <v>497.48666666666668</v>
+        <v>498.35333333333335</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -530,133 +530,136 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>3.5000000000000003E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="2">
         <f>(H4/H1)^(1/10)-1</f>
-        <v>0.1185363838155562</v>
+        <v>0.11529666051160037</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3">
-        <f>B2</f>
-        <v>5.68</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" s="3">
-        <f>ROUND((B8*$B$3) + B8,2)</f>
-        <v>6.13</v>
+        <f>B2</f>
+        <v>5.69</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="3">
-        <f t="shared" ref="B10:B18" si="0">ROUND((B9*$B$3) + B9,2)</f>
-        <v>6.62</v>
+        <f>ROUND((B9*$B$3) + B9,2)</f>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="3">
-        <f t="shared" si="0"/>
-        <v>7.15</v>
+        <f t="shared" ref="B11:B19" si="0">ROUND((B10*$B$3) + B10,2)</f>
+        <v>6.64</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="0"/>
-        <v>7.72</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="0"/>
-        <v>8.34</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="0"/>
-        <v>9.01</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="0"/>
-        <v>9.73</v>
+        <v>9.0299999999999994</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="0"/>
-        <v>10.51</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="0"/>
-        <v>11.35</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3">
+        <f t="shared" si="0"/>
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>10</v>
       </c>
-      <c r="B18" s="3">
-        <f t="shared" si="0"/>
-        <v>12.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="B19" s="3">
+        <f t="shared" si="0"/>
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="3">
-        <f>SUM(B9:B18)</f>
-        <v>88.82</v>
+      <c r="B20" s="3">
+        <f>SUM(B10:B19)</f>
+        <v>89.02000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/hw2fintools/xlsx/DivCalc.xlsx
+++ b/hw2fintools/xlsx/DivCalc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harveywargo/Desktop/GithubProjects/hw2fintools/hw2fintools/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harveywargo/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DE2588-B47F-6740-A457-1A3E95A9B941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC248377-4A34-7843-A26B-A9689DABFED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="28040" windowHeight="17180" xr2:uid="{0A3F2C1F-1553-164F-8D8B-0E0EBB5D09A0}"/>
+    <workbookView xWindow="280" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{0A3F2C1F-1553-164F-8D8B-0E0EBB5D09A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Dividend</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>BuyYield</t>
+  </si>
+  <si>
+    <t>EndGate</t>
   </si>
 </sst>
 </file>
@@ -469,7 +472,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="1">
-        <v>0.03</v>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" t="s">
@@ -477,7 +486,7 @@
       </c>
       <c r="H1" s="3">
         <f>B2/B5</f>
-        <v>167.35294117647058</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -485,14 +494,14 @@
         <v>0</v>
       </c>
       <c r="B2" s="3">
-        <v>5.69</v>
+        <v>4.96</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3">
-        <f>B19/B1</f>
-        <v>409.33333333333331</v>
+        <f>B19/E1</f>
+        <v>183.33333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -500,14 +509,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="3">
         <f>B20</f>
-        <v>89.02000000000001</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -522,7 +531,7 @@
       </c>
       <c r="H4" s="3">
         <f>SUM(H2:H3)</f>
-        <v>498.35333333333335</v>
+        <v>238.74333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -530,14 +539,14 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>3.4000000000000002E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="2">
         <f>(H4/H1)^(1/10)-1</f>
-        <v>0.11529666051160037</v>
+        <v>6.7704214020938069E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -560,7 +569,7 @@
       </c>
       <c r="B9" s="3">
         <f>B2</f>
-        <v>5.69</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -569,7 +578,7 @@
       </c>
       <c r="B10" s="3">
         <f>ROUND((B9*$B$3) + B9,2)</f>
-        <v>6.15</v>
+        <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -578,7 +587,7 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:B19" si="0">ROUND((B10*$B$3) + B10,2)</f>
-        <v>6.64</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -587,7 +596,7 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" si="0"/>
-        <v>7.17</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -596,7 +605,7 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" si="0"/>
-        <v>7.74</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -605,7 +614,7 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" si="0"/>
-        <v>8.36</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -614,7 +623,7 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" si="0"/>
-        <v>9.0299999999999994</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -623,7 +632,7 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" si="0"/>
-        <v>9.75</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -632,7 +641,7 @@
       </c>
       <c r="B17" s="3">
         <f t="shared" si="0"/>
-        <v>10.53</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -641,7 +650,7 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" si="0"/>
-        <v>11.37</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -650,7 +659,7 @@
       </c>
       <c r="B19" s="3">
         <f t="shared" si="0"/>
-        <v>12.28</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -659,7 +668,7 @@
       </c>
       <c r="B20" s="3">
         <f>SUM(B10:B19)</f>
-        <v>89.02000000000001</v>
+        <v>55.41</v>
       </c>
     </row>
   </sheetData>
